--- a/Table/TableAsset/TB_Wave.xlsx
+++ b/Table/TableAsset/TB_Wave.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="TB_Wave" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,21 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
-    <font>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
+  <fonts count="2">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -46,18 +32,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,12 +50,10 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -441,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <dimension ref="A1:O97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -543,31 +521,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[00:00~00:30] 시작</t>
+          <t>[00:00~00:30] 콤피 등장</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0.7</v>
@@ -592,15 +570,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -609,13 +587,18 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.05</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[00:30~01:00] 랩터 합류</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0.7</v>
@@ -644,7 +627,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -654,21 +637,17 @@
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>1.05</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[00:30~01:00] 오일 슬라임 합류</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0.7</v>
@@ -693,30 +672,35 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[01:00~01:30] 딜로포사우루스 합류</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0.7</v>
@@ -741,30 +725,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>1.05</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0.7</v>
@@ -793,31 +778,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_DILOPHO</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>1.1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[01:00~01:30] 3종 본격화</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0.7</v>
@@ -842,15 +823,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -859,13 +840,18 @@
         <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[01:30~02:00] 스테고사우루스 첫 등장</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0.7</v>
@@ -890,30 +876,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0.7</v>
@@ -942,31 +929,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_DILOPHO</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
         <v>1.15</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[01:30~02:00] 스파크 러너 첫 등장</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0.7</v>
@@ -995,26 +978,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_STEGO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
         <v>1.15</v>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0.7</v>
@@ -1039,33 +1023,38 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[02:00~02:30] 트리케라톱스 첫 등장</t>
+        </is>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1087,33 +1076,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>1.15</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1139,34 +1129,30 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_DILOPHO</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
         <v>1.2</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[02:00~02:30] 메탈 크러셔 첫 등장</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1192,29 +1178,30 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
         <v>1.2</v>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1236,33 +1223,38 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[02:30~03:00] 5종 혼합</t>
+        </is>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1288,34 +1280,30 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>1.25</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[02:30~03:00] 5종 혼합</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1341,29 +1329,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_DILOPHO</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
         <v>1.25</v>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1389,7 +1378,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_STEGO</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1399,19 +1388,20 @@
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
         <v>1.25</v>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1437,29 +1427,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
         <v>1.25</v>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1485,43 +1476,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
         <v>1.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[03:00~03:30] 포위 시작 - 먼 거리 스폰</t>
+          <t>[03:00] FRONT_SURGE 랩터 무리 돌격</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1538,43 +1529,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
         <v>1.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[03:00~03:30] 포위 시작 - 먼 거리 스폰</t>
+          <t>FRONT_SURGE</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -1591,38 +1582,39 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_DILOPHO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G23" t="n">
         <v>1.5</v>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
@@ -1639,34 +1631,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MON_001</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
         <v>1.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[03:30~04:00] Stoplight Striker 첫 등장</t>
+          <t>[03:30~04:00] 카르노타우루스 첫 등장</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1692,7 +1684,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MON_006</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1702,19 +1694,20 @@
         <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
         <v>1.3</v>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1736,38 +1729,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_STEGO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[04:00~04:30] 중형 혼합</t>
-        </is>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1789,33 +1778,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
-        <v>1.35</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1837,47 +1827,47 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MON_RAPTOR</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[04:00~04:30] 중형 혼합전</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>10</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MON_001</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>40</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[04:30~05:00] Wrecker/Billboard 첫 등장</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>20</v>
-      </c>
       <c r="J28" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.5</v>
@@ -1890,42 +1880,43 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MON_DILOPHO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MON_001</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>40</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>20</v>
-      </c>
       <c r="J29" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.5</v>
@@ -1938,47 +1929,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[05:00~05:30] Wrench Goblin 첫 등장</t>
-        </is>
-      </c>
+        <v>1.35</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
         <v>1.5</v>
@@ -1991,42 +1978,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MON_004</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1.35</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.5</v>
@@ -2039,11 +2027,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MON_002</t>
+          <t>MON_COMPY</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2056,25 +2044,30 @@
         <v>40</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[04:30~05:00] 프테라노돈 첫 등장</t>
+        </is>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.5</v>
@@ -2087,38 +2080,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_STEGO</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
         <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[05:30~06:00] 체력 강화 버전 전환</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -2127,7 +2116,7 @@
         <v>1.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.5</v>
@@ -2140,33 +2129,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
         <v>40</v>
       </c>
       <c r="G34" t="n">
-        <v>1.6</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2175,7 +2165,7 @@
         <v>1.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.5</v>
@@ -2188,42 +2178,43 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MON_032</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
         <v>40</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O35" t="n">
         <v>1.5</v>
@@ -2236,50 +2227,50 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[05:00~05:30] 안킬로사우루스 첫 등장</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>9</v>
       </c>
-      <c r="E36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" t="n">
-        <v>40</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[06:00] FRONT_SURGE 돌파2 (보통)</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>20</v>
-      </c>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
@@ -2289,50 +2280,46 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>FRONT_SURGE</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -2342,47 +2329,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[06:30~07:00] 강화 4종 혼합</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O38" t="n">
         <v>1.5</v>
@@ -2395,39 +2378,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MON_032</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G39" t="n">
-        <v>1.7</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
@@ -2443,11 +2427,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2457,33 +2441,33 @@
         <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[07:00~07:30] 강화 전종</t>
+          <t>[05:30~06:00] 스피노사우루스 첫 등장</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O40" t="n">
         <v>1.5</v>
@@ -2496,11 +2480,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2510,28 +2494,29 @@
         <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O41" t="n">
         <v>1.5</v>
@@ -2544,42 +2529,43 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G42" t="n">
-        <v>1.8</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O42" t="n">
         <v>1.5</v>
@@ -2592,39 +2578,40 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
@@ -2640,45 +2627,50 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[06:00] FRONT_SURGE 트리케라톱스 돌진</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2688,45 +2680,50 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>FRONT_SURGE</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2736,45 +2733,46 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_RAPTOR</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G46" t="n">
-        <v>2.2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2784,42 +2782,47 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_STEGO</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[06:30~07:00] 대형 공룡 혼합</t>
+        </is>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M47" t="n">
         <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O47" t="n">
         <v>1.5</v>
@@ -2832,42 +2835,43 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G48" t="n">
-        <v>2.2</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.5</v>
@@ -2880,38 +2884,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[08:30~09:00] 최종 돌파 직전</t>
-        </is>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L49" t="n">
         <v>4</v>
@@ -2920,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O49" t="n">
         <v>1.5</v>
@@ -2933,11 +2933,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2947,28 +2947,29 @@
         <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O50" t="n">
         <v>1.5</v>
@@ -2981,42 +2982,47 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
         <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[07:00~07:30] 전종 혼합</t>
+        </is>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
         <v>2</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O51" t="n">
         <v>1.5</v>
@@ -3029,11 +3035,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3043,28 +3049,29 @@
         <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G52" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O52" t="n">
         <v>1.5</v>
@@ -3077,50 +3084,46 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>FRONT_SURGE</t>
-        </is>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54">
@@ -3130,50 +3133,46 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>FRONT_SURGE</t>
-        </is>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="55">
@@ -3183,11 +3182,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3197,28 +3196,29 @@
         <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G55" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O55" t="n">
         <v>1.5</v>
@@ -3231,42 +3231,47 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MON_027</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G56" t="n">
-        <v>2.8</v>
+        <v>2</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[07:30~08:00] 고난이도 혼합</t>
+        </is>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" t="n">
         <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O56" t="n">
         <v>1.5</v>
@@ -3279,42 +3284,43 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G57" t="n">
-        <v>2.8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O57" t="n">
         <v>1.5</v>
@@ -3327,44 +3333,40 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MON_028</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[10:00~11:00] Extension 쉬움</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -3380,39 +3382,40 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -3428,33 +3431,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MON_035</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3463,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O60" t="n">
         <v>1.5</v>
@@ -3476,42 +3480,47 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G61" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[08:00~08:30] 압박 증가</t>
+        </is>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M61" t="n">
         <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O61" t="n">
         <v>1.5</v>
@@ -3524,42 +3533,43 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MON_034</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>3.8</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
         <v>0.85</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
         <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O62" t="n">
         <v>1.5</v>
@@ -3572,30 +3582,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MON_035</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G63" t="n">
-        <v>3.8</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
         <v>0.85</v>
@@ -3620,45 +3631,46 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="65">
@@ -3668,33 +3680,34 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MON_035</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3703,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="66">
@@ -3716,45 +3729,50 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MON_030</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G66" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[08:30~09:00] 최종 돌파 직전</t>
+        </is>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O66" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="67">
@@ -3764,45 +3782,46 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MON_034</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G67" t="n">
-        <v>8</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="68">
@@ -3812,11 +3831,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MON_035</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3826,19 +3845,20 @@
         <v>4</v>
       </c>
       <c r="F68" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G68" t="n">
-        <v>8</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3850,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="69">
@@ -3860,33 +3880,34 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>18</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MON_SPINO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>65</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
         <v>7</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>MON_008</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" t="n">
-        <v>40</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I69" t="n">
-        <v>20</v>
-      </c>
       <c r="J69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3908,33 +3929,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G70" t="n">
-        <v>1.35</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3943,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>1.5</v>
@@ -3956,45 +3978,50 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G71" t="n">
-        <v>1.4</v>
+        <v>3</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[09:00] FRONT_SURGE 대형 공룡 총공격</t>
+        </is>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O71" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4004,45 +4031,50 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>19</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MON_SPINO</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>80</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>FRONT_SURGE</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L72" t="n">
         <v>10</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MON_008</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" t="n">
-        <v>40</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I72" t="n">
-        <v>20</v>
-      </c>
-      <c r="J72" t="n">
-        <v>50</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O72" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4052,45 +4084,50 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G73" t="n">
-        <v>1.5</v>
+        <v>3</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>FRONT_SURGE</t>
+        </is>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4100,42 +4137,47 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G74" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>[09:30~10:00] 최종 전종 강화</t>
+        </is>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O74" t="n">
         <v>1.5</v>
@@ -4148,42 +4190,43 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G75" t="n">
-        <v>1.6</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O75" t="n">
         <v>1.5</v>
@@ -4196,33 +4239,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G76" t="n">
-        <v>1.65</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -4244,33 +4288,34 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>4</v>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G77" t="n">
-        <v>1.7</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4292,33 +4337,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
         <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G78" t="n">
-        <v>1.75</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4327,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
         <v>1.5</v>
@@ -4340,42 +4386,47 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G79" t="n">
-        <v>1.8</v>
+        <v>3</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>[10:00~11:00] Extension 쉬움</t>
+        </is>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>1.5</v>
@@ -4388,42 +4439,43 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G80" t="n">
-        <v>1.85</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O80" t="n">
         <v>1.5</v>
@@ -4436,33 +4488,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G81" t="n">
-        <v>1.9</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4471,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O81" t="n">
         <v>1.5</v>
@@ -4484,33 +4537,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MON_008</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G82" t="n">
-        <v>1.95</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4519,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
         <v>1.5</v>
@@ -4532,42 +4586,47 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G83" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>[11:00~12:00] Extension 보통</t>
+        </is>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O83" t="n">
         <v>1.5</v>
@@ -4580,42 +4639,43 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>22</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MON_CARNO</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>90</v>
+      </c>
+      <c r="G84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" t="n">
         <v>8</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MON_009</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" t="n">
-        <v>4</v>
-      </c>
-      <c r="F84" t="n">
-        <v>40</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I84" t="n">
-        <v>20</v>
-      </c>
-      <c r="J84" t="n">
-        <v>50</v>
-      </c>
       <c r="K84" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O84" t="n">
         <v>1.5</v>
@@ -4628,33 +4688,34 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G85" t="n">
-        <v>1.4</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4663,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
         <v>1.5</v>
@@ -4676,33 +4737,34 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G86" t="n">
-        <v>1.45</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4711,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
         <v>1.5</v>
@@ -4724,33 +4786,34 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
         <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G87" t="n">
-        <v>1.5</v>
-      </c>
+        <v>3.8</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4759,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O87" t="n">
         <v>1.5</v>
@@ -4772,45 +4835,50 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>1.55</v>
+        <v>5</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>[12:00~13:00] Extension 어려움</t>
+        </is>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K88" t="n">
         <v>0.5</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N88" t="n">
+        <v>3</v>
+      </c>
+      <c r="O88" t="n">
         <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="89">
@@ -4820,45 +4888,46 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>1.6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K89" t="n">
         <v>0.5</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N89" t="n">
+        <v>3</v>
+      </c>
+      <c r="O89" t="n">
         <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="90">
@@ -4868,30 +4937,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>1.65</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
         <v>0.5</v>
@@ -4903,10 +4973,10 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O90" t="n">
         <v>1</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="91">
@@ -4916,30 +4986,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
         <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>1.7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
         <v>0.5</v>
@@ -4951,10 +5022,10 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O91" t="n">
         <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="92">
@@ -4964,30 +5035,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
         <v>4</v>
       </c>
       <c r="F92" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G92" t="n">
-        <v>1.75</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="K92" t="n">
         <v>0.5</v>
@@ -4999,10 +5071,10 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="n">
         <v>1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="93">
@@ -5012,45 +5084,50 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_TRIKE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="G93" t="n">
-        <v>1.8</v>
+        <v>8</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>[13:00~] 즉사 구간</t>
+        </is>
       </c>
       <c r="I93" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K93" t="n">
         <v>0.5</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="94">
@@ -5060,45 +5137,46 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_SPINO</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="G94" t="n">
-        <v>1.85</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
         <v>0.5</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="95">
@@ -5108,30 +5186,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_ANKYLO</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="G95" t="n">
-        <v>1.9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
         <v>0.5</v>
@@ -5143,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96">
@@ -5156,45 +5235,46 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MON_009</t>
+          <t>MON_CARNO</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>40</v>
+        <v>999</v>
       </c>
       <c r="G96" t="n">
-        <v>1.95</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K96" t="n">
         <v>0.5</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97">
@@ -5204,35 +5284,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MON_003</t>
+          <t>MON_PTERO</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>60</v>
+        <v>999</v>
       </c>
       <c r="G97" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K97" t="n">
         <v>0.5</v>
@@ -5244,434 +5320,10 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O97" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>5</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>MON_007</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="n">
-        <v>28</v>
-      </c>
-      <c r="F98" t="n">
-        <v>60</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>15</v>
-      </c>
-      <c r="J98" t="n">
-        <v>20</v>
-      </c>
-      <c r="K98" t="n">
         <v>0.5</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>7</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>MON_005</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="n">
-        <v>28</v>
-      </c>
-      <c r="F99" t="n">
-        <v>60</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>15</v>
-      </c>
-      <c r="J99" t="n">
-        <v>20</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>9</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>MON_003</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="n">
-        <v>28</v>
-      </c>
-      <c r="F100" t="n">
-        <v>60</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>15</v>
-      </c>
-      <c r="J100" t="n">
-        <v>20</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>11</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>MON_007</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="n">
-        <v>28</v>
-      </c>
-      <c r="F101" t="n">
-        <v>60</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>15</v>
-      </c>
-      <c r="J101" t="n">
-        <v>20</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>1</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>13</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>MON_029</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>28</v>
-      </c>
-      <c r="F102" t="n">
-        <v>60</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>15</v>
-      </c>
-      <c r="J102" t="n">
-        <v>20</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>1</v>
-      </c>
-      <c r="O102" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>15</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>MON_033</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" t="n">
-        <v>28</v>
-      </c>
-      <c r="F103" t="n">
-        <v>60</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" t="n">
-        <v>20</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>1</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>17</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>MON_031</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" t="n">
-        <v>28</v>
-      </c>
-      <c r="F104" t="n">
-        <v>60</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>15</v>
-      </c>
-      <c r="J104" t="n">
-        <v>20</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1</v>
-      </c>
-      <c r="O104" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>WG_CH1</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>19</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MON_029</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>28</v>
-      </c>
-      <c r="F105" t="n">
-        <v>60</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>MINIBOSS</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>15</v>
-      </c>
-      <c r="J105" t="n">
-        <v>20</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>1</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1.5</v>
       </c>
     </row>
   </sheetData>
